--- a/data/pediatric.xlsx
+++ b/data/pediatric.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1088,6 +1088,23 @@
       <c r="C36" s="6" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ageRange</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Supported / validated age range</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>children, adolescents</t>
         </is>
       </c>
     </row>
@@ -1102,13 +1119,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1903,16 +1920,38 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Warning: never rename column A (criterion_id) — it is the key read by the web page. You can freely add / remove pipeline columns in the 'Pipelines' sheet.</t>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>ageRange</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Supported / validated age range</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Free text, e.g. 'neonates, infants' or 'children, adolescents' (used by the age-range question)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Warning: never rename column A (criterion_id) — it is the key read by the web page. You can freely add / remove pipeline columns in the 'Pipelines' sheet, and add extra criterion rows here — any row not used by the shared engine is passed through as raw text and can be read by this category's own questions.js logic.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
